--- a/satisfaction_surveys/007_enterprise_healthcare_client_insights_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/007_enterprise_healthcare_client_insights_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1332,8 +1332,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1378,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'save_and_continue'}</t>
+          <t>save_and_continue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Save and Continue'}</t>
+          <t>Save and Continue</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1395,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1429,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1463,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'for_referral'}</t>
+          <t>for_referral</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'For Referral'}</t>
+          <t>For Referral</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_for_referral'}</t>
+          <t>not_for_referral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not for Referral'}</t>
+          <t>Not for Referral</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1497,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'maybe_for_referral'}</t>
+          <t>maybe_for_referral</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Maybe for Referral'}</t>
+          <t>Maybe for Referral</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_google'}</t>
+          <t>referrals_from_google</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Google'}</t>
+          <t>Referrals from Google</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_social_media'}</t>
+          <t>referrals_from_social_media</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Social Media'}</t>
+          <t>Referrals from Social Media</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_word_of_mouth'}</t>
+          <t>referrals_from_word_of_mouth</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Word of Mouth'}</t>
+          <t>Referrals from Word of Mouth</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1565,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_email'}</t>
+          <t>referrals_from_email</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Email'}</t>
+          <t>Referrals from Email</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_other'}</t>
+          <t>referrals_from_other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Other'}</t>
+          <t>Referrals from Other</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_google'}</t>
+          <t>referrals_from_google</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Google'}</t>
+          <t>Referrals from Google</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_social_media'}</t>
+          <t>referrals_from_social_media</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Social Media'}</t>
+          <t>Referrals from Social Media</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_word_of_mouth'}</t>
+          <t>referrals_from_word_of_mouth</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Word of Mouth'}</t>
+          <t>Referrals from Word of Mouth</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_email'}</t>
+          <t>referrals_from_email</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Email'}</t>
+          <t>Referrals from Email</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_other'}</t>
+          <t>referrals_from_other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Other'}</t>
+          <t>Referrals from Other</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_google'}</t>
+          <t>referrals_from_google</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Google'}</t>
+          <t>Referrals from Google</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_social_media'}</t>
+          <t>referrals_from_social_media</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Social Media'}</t>
+          <t>Referrals from Social Media</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_word_of_mouth'}</t>
+          <t>referrals_from_word_of_mouth</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Word of Mouth'}</t>
+          <t>Referrals from Word of Mouth</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_email'}</t>
+          <t>referrals_from_email</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Email'}</t>
+          <t>Referrals from Email</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_other'}</t>
+          <t>referrals_from_other</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Other'}</t>
+          <t>Referrals from Other</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_google'}</t>
+          <t>referrals_from_google</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Google'}</t>
+          <t>Referrals from Google</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_social_media'}</t>
+          <t>referrals_from_social_media</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Social Media'}</t>
+          <t>Referrals from Social Media</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_word_of_mouth'}</t>
+          <t>referrals_from_word_of_mouth</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Word of Mouth'}</t>
+          <t>Referrals from Word of Mouth</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_email'}</t>
+          <t>referrals_from_email</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Email'}</t>
+          <t>Referrals from Email</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_other'}</t>
+          <t>referrals_from_other</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Other'}</t>
+          <t>Referrals from Other</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_google'}</t>
+          <t>referrals_from_google</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Google'}</t>
+          <t>Referrals from Google</t>
         </is>
       </c>
     </row>
@@ -2143,12 +2143,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_social_media'}</t>
+          <t>referrals_from_social_media</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Social Media'}</t>
+          <t>Referrals from Social Media</t>
         </is>
       </c>
     </row>
@@ -2160,12 +2160,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_word_of_mouth'}</t>
+          <t>referrals_from_word_of_mouth</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Word of Mouth'}</t>
+          <t>Referrals from Word of Mouth</t>
         </is>
       </c>
     </row>
@@ -2177,12 +2177,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_email'}</t>
+          <t>referrals_from_email</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Email'}</t>
+          <t>Referrals from Email</t>
         </is>
       </c>
     </row>
@@ -2194,12 +2194,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_other'}</t>
+          <t>referrals_from_other</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Other'}</t>
+          <t>Referrals from Other</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -2228,12 +2228,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -2245,12 +2245,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -2262,12 +2262,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'In Person'}</t>
+          <t>In Person</t>
         </is>
       </c>
     </row>
@@ -2279,12 +2279,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_google'}</t>
+          <t>referrals_from_google</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Google'}</t>
+          <t>Referrals from Google</t>
         </is>
       </c>
     </row>
@@ -2296,12 +2296,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_social_media'}</t>
+          <t>referrals_from_social_media</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Social Media'}</t>
+          <t>Referrals from Social Media</t>
         </is>
       </c>
     </row>
@@ -2313,12 +2313,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_word_of_mouth'}</t>
+          <t>referrals_from_word_of_mouth</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Word of Mouth'}</t>
+          <t>Referrals from Word of Mouth</t>
         </is>
       </c>
     </row>
@@ -2330,12 +2330,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_email'}</t>
+          <t>referrals_from_email</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Email'}</t>
+          <t>Referrals from Email</t>
         </is>
       </c>
     </row>
@@ -2347,12 +2347,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'referrals_from_other'}</t>
+          <t>referrals_from_other</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Referrals from Other'}</t>
+          <t>Referrals from Other</t>
         </is>
       </c>
     </row>
@@ -2364,12 +2364,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'save_and_continue'}</t>
+          <t>save_and_continue</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Save and Continue'}</t>
+          <t>Save and Continue</t>
         </is>
       </c>
     </row>
@@ -2398,12 +2398,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'cancel'}</t>
+          <t>cancel</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'Cancel'}</t>
+          <t>Cancel</t>
         </is>
       </c>
     </row>
